--- a/table/supp/workbooks/SuppTable_S8_CTL_LIN_candidate_overlap.xlsx
+++ b/table/supp/workbooks/SuppTable_S8_CTL_LIN_candidate_overlap.xlsx
@@ -2091,7 +2091,7 @@
         <v>1100</v>
       </c>
       <c r="C3" t="n">
-        <v>4323</v>
+        <v>4319</v>
       </c>
       <c r="D3" t="n">
         <v>289</v>
@@ -2100,19 +2100,19 @@
         <v>811</v>
       </c>
       <c r="F3" t="n">
-        <v>4034</v>
+        <v>4030</v>
       </c>
       <c r="G3" t="n">
-        <v>139.750786140418</v>
+        <v>139.621477062333</v>
       </c>
       <c r="H3" t="n">
-        <v>2.06796690009043</v>
+        <v>2.06988212759688</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0562913907284768</v>
+        <v>0.0563352826510721</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0000000000000000000000000000000000428183565678891</v>
+        <v>0.0000000000000000000000000000000000362379371568146</v>
       </c>
     </row>
     <row r="4">
@@ -2236,22 +2236,22 @@
         <v>521</v>
       </c>
       <c r="E3" t="n">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="F3" t="n">
         <v>193</v>
       </c>
       <c r="G3" t="n">
-        <v>168.217175887696</v>
+        <v>168.002064409579</v>
       </c>
       <c r="H3" t="n">
-        <v>1.14732635940131</v>
+        <v>1.14879540723665</v>
       </c>
       <c r="I3" t="n">
-        <v>0.102008456659619</v>
+        <v>0.102116402116402</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00845810722515912</v>
+        <v>0.00797212193076201</v>
       </c>
     </row>
     <row r="4">
@@ -2332,22 +2332,22 @@
         <v>378</v>
       </c>
       <c r="E6" t="n">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F6" t="n">
         <v>168</v>
       </c>
       <c r="G6" t="n">
-        <v>161.05221588416</v>
+        <v>160.886353663888</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0431399473624</v>
+        <v>1.04421534936999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.14225232853514</v>
+        <v>0.142372881355932</v>
       </c>
       <c r="J6" t="n">
-        <v>0.231133524674648</v>
+        <v>0.225405848168091</v>
       </c>
     </row>
     <row r="7">
@@ -2996,7 +2996,7 @@
         <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -8804,7 +8804,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -8813,10 +8813,10 @@
         <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01298968466218</v>
+        <v>0.0106973873688541</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -10712,7 +10712,7 @@
         <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E66" t="n">
         <v>0.00000000000003522187</v>
